--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A90B43-39A6-4E28-ABE5-8DF4B7FCE3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E5F425-9B1E-4E64-8C83-06239A9E5960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="2544" yWindow="2712" windowWidth="16872" windowHeight="10248" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
-    <sheet name="SE仕様" sheetId="1" r:id="rId2"/>
+    <sheet name="サウンド表" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -159,9 +159,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>break.mp3</t>
-  </si>
-  <si>
     <t>岩を壊したときの音</t>
     <rPh sb="0" eb="1">
       <t>イワ</t>
@@ -362,22 +359,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>この時岩を壊したときの音はならない</t>
-    <rPh sb="2" eb="3">
-      <t>トキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>イワ</t>
-    </rPh>
-    <rPh sb="5" eb="6">
-      <t>コワ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>オト</t>
-    </rPh>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>タイトル</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -399,15 +380,208 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>A_silver_linging.mp3</t>
-  </si>
-  <si>
     <t>タイトルシーンに入ったら流します</t>
     <rPh sb="8" eb="9">
       <t>ハイ</t>
     </rPh>
     <rPh sb="12" eb="13">
       <t>ナガ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>この時「岩を壊したときの音」はならない</t>
+    <rPh sb="2" eb="3">
+      <t>トキ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>イワ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>コワ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>スライムが突進するときになる音</t>
+    <rPh sb="5" eb="7">
+      <t>トッシン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>通常の移動では鳴らない</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ナ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>attack_slime.mp3</t>
+  </si>
+  <si>
+    <t>BGM_title.mp3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>洞窟</t>
+  </si>
+  <si>
+    <t>洞窟</t>
+    <rPh sb="0" eb="2">
+      <t>ドウクツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>繁茂した洞窟</t>
+    <rPh sb="0" eb="2">
+      <t>ハンモ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウクツ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>地下水洞</t>
+    <rPh sb="0" eb="4">
+      <t>チカスイドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶岩洞</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウガン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ドウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遺跡</t>
+    <rPh sb="0" eb="2">
+      <t>イセキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BGM_ruins.mp3</t>
+  </si>
+  <si>
+    <t>BGM_underground water cave.mp3</t>
+  </si>
+  <si>
+    <t>BGM_cave.mp3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>BGM_Overgrown cave.mp3</t>
+  </si>
+  <si>
+    <t>BGM_lava tube.mp3</t>
+  </si>
+  <si>
+    <t>bubble.mp3</t>
+  </si>
+  <si>
+    <t>洞窟マップの時になります</t>
+    <rPh sb="0" eb="2">
+      <t>ドウクツ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>繫茂した洞窟マップの時になります</t>
+    <rPh sb="0" eb="2">
+      <t>ハンモ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ドウクツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>地下水洞マップの時になります</t>
+    <rPh sb="0" eb="4">
+      <t>チカスイドウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶岩洞マップの時になります</t>
+    <rPh sb="0" eb="3">
+      <t>ヨウガンドウ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶岩マップでランダムな時になります</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウガン</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>溶岩のはじける音です</t>
+    <rPh sb="0" eb="2">
+      <t>ヨウガン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>オト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>遺跡マップの時になります</t>
+    <rPh sb="0" eb="2">
+      <t>イセキ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>トキ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>田中</t>
+    <rPh sb="0" eb="2">
+      <t>タナカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>新規作成</t>
+    <rPh sb="0" eb="4">
+      <t>シンキサクセイ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -505,7 +679,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -524,13 +698,28 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -568,6 +757,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -884,22 +1079,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
-  <dimension ref="B1:H4"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <dimension ref="B1:H5"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="5.3125" customWidth="1"/>
-    <col min="6" max="6" width="7.3125" customWidth="1"/>
-    <col min="7" max="7" width="11.8125" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.796875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -911,6 +1106,20 @@
       </c>
       <c r="H4" s="2" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="E5" s="14">
+        <v>46077</v>
+      </c>
+      <c r="F5" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -921,19 +1130,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
-  <dimension ref="A1:J33"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:J28"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
-    <col min="8" max="8" width="20.4375" customWidth="1"/>
-    <col min="9" max="9" width="35.375" customWidth="1"/>
-    <col min="10" max="10" width="32.125" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" customWidth="1"/>
+    <col min="7" max="7" width="13.09765625" customWidth="1"/>
+    <col min="8" max="8" width="32" customWidth="1"/>
+    <col min="9" max="9" width="35.3984375" customWidth="1"/>
+    <col min="10" max="10" width="34.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:10" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -945,25 +1154,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="11.45" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="25.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
@@ -977,128 +1186,279 @@
         <v>13</v>
       </c>
       <c r="J9" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F10" s="13" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="I10" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="13"/>
+    </row>
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F11" s="13"/>
+      <c r="G11" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H11" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J11" s="13"/>
+    </row>
+    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F12" s="13"/>
+      <c r="G12" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" s="13"/>
+    </row>
+    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F13" s="13"/>
+      <c r="G13" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="J13" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H14" s="13" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F10" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="I14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="J14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F15" s="13"/>
+      <c r="G15" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H11" t="s">
-        <v>19</v>
-      </c>
-      <c r="I11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H13" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" t="s">
+      <c r="H15" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I15" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="J15" s="13"/>
+    </row>
+    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F16" s="13"/>
+      <c r="G16" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="I16" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="J16" s="13"/>
+    </row>
+    <row r="17" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F17" s="13"/>
+      <c r="G17" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="I17" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="J17" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="18" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F18" s="13"/>
+      <c r="G18" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="I18" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="J18" s="13" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F19" s="13"/>
+      <c r="G19" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="J19" s="13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F20" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="G20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="I20" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="J20" s="13"/>
+    </row>
+    <row r="21" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F21" s="13"/>
+      <c r="G21" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J21" s="13"/>
+    </row>
+    <row r="22" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F22" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I22" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="J22" s="13"/>
+    </row>
+    <row r="23" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F23" s="13"/>
+      <c r="G23" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="J13" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H14" t="s">
-        <v>28</v>
-      </c>
-      <c r="I14" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H15" t="s">
-        <v>32</v>
-      </c>
-      <c r="I15" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H16" t="s">
-        <v>33</v>
-      </c>
-      <c r="I16" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H17" t="s">
-        <v>35</v>
-      </c>
-      <c r="I17" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H18" t="s">
-        <v>37</v>
-      </c>
-      <c r="I18" t="s">
-        <v>38</v>
-      </c>
-      <c r="J18" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F19" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" t="s">
+      <c r="I23" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="13"/>
+    </row>
+    <row r="24" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F24" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J24" s="13"/>
+    </row>
+    <row r="25" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F25" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I25" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="J25" s="13"/>
+    </row>
+    <row r="26" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F26" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="G26" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I26" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J26" s="13"/>
+    </row>
+    <row r="27" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F27" s="13"/>
+      <c r="G27" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H19" t="s">
+      <c r="H27" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I27" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="28" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F28" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G28" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="I19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="G20" t="s">
-        <v>43</v>
-      </c>
-      <c r="H20" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="8:9" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="H33" t="s">
-        <v>25</v>
-      </c>
-      <c r="I33" t="s">
-        <v>26</v>
-      </c>
+      <c r="H28" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J28" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9E5F425-9B1E-4E64-8C83-06239A9E5960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85FCEF3-969F-45B1-95C4-98C1BE802279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2544" yWindow="2712" windowWidth="16872" windowHeight="10248" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F85FCEF3-969F-45B1-95C4-98C1BE802279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12F2417-4227-4199-9422-1DF906249FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2544" yWindow="2712" windowWidth="16872" windowHeight="10248" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -582,6 +582,46 @@
     <t>新規作成</t>
     <rPh sb="0" eb="4">
       <t>シンキサクセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>clause_book.mp3</t>
+  </si>
+  <si>
+    <t>open_book.mp3</t>
+  </si>
+  <si>
+    <t>説明テロップを開いたとき</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ヒラ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>説明テロップを閉じたとき</t>
+    <rPh sb="0" eb="2">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ト</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>追加</t>
+    <rPh sb="0" eb="2">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SE追加</t>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
@@ -719,7 +759,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -763,6 +803,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1079,22 +1122,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
-  <dimension ref="B1:H5"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="B1:H6"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="5" max="5" width="11.19921875" customWidth="1"/>
-    <col min="6" max="6" width="7.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.796875" customWidth="1"/>
+    <col min="5" max="5" width="11.1875" customWidth="1"/>
+    <col min="6" max="6" width="7.3125" customWidth="1"/>
+    <col min="7" max="7" width="11.8125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1108,18 +1151,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="E5" s="14">
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E5" s="15">
         <v>46077</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H5" t="s">
+      <c r="H5" s="13" t="s">
         <v>68</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="E6" s="15">
+        <v>46091</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -1130,19 +1187,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
-  <dimension ref="A1:J28"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" customWidth="1"/>
-    <col min="7" max="7" width="13.09765625" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="13.125" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="35.3984375" customWidth="1"/>
-    <col min="10" max="10" width="34.8984375" customWidth="1"/>
+    <col min="9" max="9" width="35.375" customWidth="1"/>
+    <col min="10" max="10" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:10" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1154,25 +1211,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="11.4" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:10" ht="11.45" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="7" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:10" ht="25.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
@@ -1189,7 +1246,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F10" s="13" t="s">
         <v>15</v>
       </c>
@@ -1204,7 +1261,7 @@
       </c>
       <c r="J10" s="13"/>
     </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
         <v>16</v>
@@ -1217,7 +1274,7 @@
       </c>
       <c r="J11" s="13"/>
     </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
         <v>16</v>
@@ -1230,7 +1287,7 @@
       </c>
       <c r="J12" s="13"/>
     </row>
-    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>16</v>
@@ -1245,7 +1302,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
         <v>16</v>
@@ -1258,7 +1315,7 @@
       </c>
       <c r="J14" s="13"/>
     </row>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F15" s="13"/>
       <c r="G15" s="13" t="s">
         <v>16</v>
@@ -1271,7 +1328,7 @@
       </c>
       <c r="J15" s="13"/>
     </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="s">
         <v>16</v>
@@ -1284,7 +1341,7 @@
       </c>
       <c r="J16" s="13"/>
     </row>
-    <row r="17" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F17" s="13"/>
       <c r="G17" s="13" t="s">
         <v>16</v>
@@ -1299,7 +1356,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F18" s="13"/>
       <c r="G18" s="13" t="s">
         <v>16</v>
@@ -1314,7 +1371,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="19" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F19" s="13"/>
       <c r="G19" s="13" t="s">
         <v>16</v>
@@ -1329,136 +1386,174 @@
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F20" s="13" t="s">
-        <v>38</v>
-      </c>
+    <row r="20" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A20" s="14">
+        <v>46091</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>47</v>
+        <v>70</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>42</v>
+        <v>71</v>
       </c>
       <c r="J20" s="13"/>
     </row>
-    <row r="21" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A21" s="14">
+        <v>46091</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>73</v>
+      </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>39</v>
+        <v>69</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="J21" s="13"/>
     </row>
-    <row r="22" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F22" s="13" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="J22" s="13"/>
     </row>
-    <row r="23" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="J23" s="13"/>
     </row>
-    <row r="24" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F24" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J24" s="13"/>
     </row>
-    <row r="25" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F25" s="13" t="s">
-        <v>51</v>
-      </c>
+    <row r="25" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F25" s="13"/>
       <c r="G25" s="13" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>62</v>
+        <v>25</v>
       </c>
       <c r="J25" s="13"/>
     </row>
-    <row r="26" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F26" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G26" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="J26" s="13"/>
     </row>
-    <row r="27" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F27" s="13"/>
+    <row r="27" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F27" s="13" t="s">
+        <v>51</v>
+      </c>
       <c r="G27" s="13" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="J27" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="6:10" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+        <v>62</v>
+      </c>
+      <c r="J27" s="13"/>
+    </row>
+    <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F28" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H28" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="I28" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J28" s="13"/>
+    </row>
+    <row r="29" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F29" s="13"/>
+      <c r="G29" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F30" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="I28" s="13" t="s">
+      <c r="I30" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="J28" s="13"/>
+      <c r="J30" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー (2)\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12F2417-4227-4199-9422-1DF906249FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF65A6C1-DB5F-49D8-AC02-CE1986B236DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -823,6 +823,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>2424113</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>71437</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>2652713</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="直線コネクタ 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8F596BC2-C6C1-4DC7-A036-AF9FC2602B99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8110538" y="2971800"/>
+          <a:ext cx="5362575" cy="9525"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="dk1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="dk1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1559,5 +1614,6 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー (2)\Document\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF65A6C1-DB5F-49D8-AC02-CE1986B236DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4530CA-BE6D-469D-B9BA-E65EA6160D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -437,9 +437,6 @@
   </si>
   <si>
     <t>洞窟</t>
-  </si>
-  <si>
-    <t>洞窟</t>
     <rPh sb="0" eb="2">
       <t>ドウクツ</t>
     </rPh>
@@ -623,6 +620,21 @@
     <rPh sb="2" eb="4">
       <t>ツイカ</t>
     </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>break.mp3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>実装</t>
+    <rPh sb="0" eb="2">
+      <t>ジッソウ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>OK</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1178,21 +1190,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
   <dimension ref="B1:H6"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="5" max="5" width="11.1875" customWidth="1"/>
-    <col min="6" max="6" width="7.3125" customWidth="1"/>
-    <col min="7" max="7" width="11.8125" customWidth="1"/>
+    <col min="5" max="5" width="11.19921875" customWidth="1"/>
+    <col min="6" max="6" width="7.296875" customWidth="1"/>
+    <col min="7" max="7" width="11.796875" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1206,32 +1218,32 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E5" s="15">
         <v>46077</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E6" s="15">
         <v>46091</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1242,19 +1254,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
+  <dimension ref="A1:K30"/>
+  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
-    <col min="6" max="6" width="14.125" customWidth="1"/>
-    <col min="7" max="7" width="13.125" customWidth="1"/>
+    <col min="6" max="6" width="14.09765625" customWidth="1"/>
+    <col min="7" max="7" width="13.09765625" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="35.375" customWidth="1"/>
-    <col min="10" max="10" width="34.875" customWidth="1"/>
+    <col min="9" max="9" width="35.3984375" customWidth="1"/>
+    <col min="10" max="10" width="34.8984375" customWidth="1"/>
+    <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1266,25 +1279,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="3" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="11.45" customHeight="1" x14ac:dyDescent="0.7"/>
-    <row r="7" spans="1:10" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="6" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="25.25" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="9" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
@@ -1300,8 +1313,11 @@
       <c r="J9" s="12" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K9" s="12" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F10" s="13" t="s">
         <v>15</v>
       </c>
@@ -1309,14 +1325,15 @@
         <v>16</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>17</v>
       </c>
       <c r="J10" s="13"/>
-    </row>
-    <row r="11" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K10" s="13"/>
+    </row>
+    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
         <v>16</v>
@@ -1328,8 +1345,9 @@
         <v>19</v>
       </c>
       <c r="J11" s="13"/>
-    </row>
-    <row r="12" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K11" s="13"/>
+    </row>
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
         <v>16</v>
@@ -1341,8 +1359,9 @@
         <v>21</v>
       </c>
       <c r="J12" s="13"/>
-    </row>
-    <row r="13" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K12" s="13"/>
+    </row>
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>16</v>
@@ -1356,8 +1375,9 @@
       <c r="J13" s="13" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K13" s="13"/>
+    </row>
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
         <v>16</v>
@@ -1369,8 +1389,9 @@
         <v>28</v>
       </c>
       <c r="J14" s="13"/>
-    </row>
-    <row r="15" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K14" s="13"/>
+    </row>
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F15" s="13"/>
       <c r="G15" s="13" t="s">
         <v>16</v>
@@ -1382,8 +1403,9 @@
         <v>30</v>
       </c>
       <c r="J15" s="13"/>
-    </row>
-    <row r="16" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K15" s="13"/>
+    </row>
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="s">
         <v>16</v>
@@ -1395,8 +1417,9 @@
         <v>33</v>
       </c>
       <c r="J16" s="13"/>
-    </row>
-    <row r="17" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F17" s="13"/>
       <c r="G17" s="13" t="s">
         <v>16</v>
@@ -1410,8 +1433,9 @@
       <c r="J17" s="13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F18" s="13"/>
       <c r="G18" s="13" t="s">
         <v>16</v>
@@ -1425,8 +1449,9 @@
       <c r="J18" s="13" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K18" s="13"/>
+    </row>
+    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F19" s="13"/>
       <c r="G19" s="13" t="s">
         <v>16</v>
@@ -1440,46 +1465,49 @@
       <c r="J19" s="13" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="14">
         <v>46091</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="13" t="s">
-        <v>71</v>
-      </c>
       <c r="J20" s="13"/>
-    </row>
-    <row r="21" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K20" s="13"/>
+    </row>
+    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="14">
         <v>46091</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J21" s="13"/>
-    </row>
-    <row r="22" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F22" s="13" t="s">
         <v>38</v>
       </c>
@@ -1493,8 +1521,11 @@
         <v>42</v>
       </c>
       <c r="J22" s="13"/>
-    </row>
-    <row r="23" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K22" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F23" s="13"/>
       <c r="G23" s="13" t="s">
         <v>16</v>
@@ -1506,109 +1537,119 @@
         <v>40</v>
       </c>
       <c r="J23" s="13"/>
-    </row>
-    <row r="24" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K23" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F24" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G24" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13"/>
+    </row>
+    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F25" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="H25" s="13" t="s">
         <v>56</v>
       </c>
-      <c r="I24" s="13" t="s">
+      <c r="I25" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="J24" s="13"/>
-    </row>
-    <row r="25" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F25" s="13"/>
-      <c r="G25" s="13" t="s">
+      <c r="J25" s="13"/>
+      <c r="K25" s="13"/>
+    </row>
+    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F26" s="13"/>
+      <c r="G26" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H25" s="13" t="s">
+      <c r="H26" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="I25" s="13" t="s">
+      <c r="I26" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="J25" s="13"/>
-    </row>
-    <row r="26" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F26" s="13" t="s">
+      <c r="J26" s="13"/>
+      <c r="K26" s="13"/>
+    </row>
+    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F27" s="13" t="s">
         <v>50</v>
-      </c>
-      <c r="G26" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H26" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="J26" s="13"/>
-    </row>
-    <row r="27" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="F27" s="13" t="s">
-        <v>51</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J27" s="13"/>
-    </row>
-    <row r="28" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K27" s="13"/>
+    </row>
+    <row r="28" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F28" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J28" s="13"/>
-    </row>
-    <row r="29" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K28" s="13"/>
+    </row>
+    <row r="29" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F29" s="13"/>
       <c r="G29" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="I29" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="J29" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="J29" s="13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F30" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>41</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I30" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4530CA-BE6D-469D-B9BA-E65EA6160D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBDB404-1245-48A6-8E78-5278EECC75EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -1485,7 +1485,9 @@
         <v>70</v>
       </c>
       <c r="J20" s="13"/>
-      <c r="K20" s="13"/>
+      <c r="K20" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="14">
@@ -1505,7 +1507,9 @@
         <v>71</v>
       </c>
       <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
+      <c r="K21" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F22" s="13" t="s">

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CBDB404-1245-48A6-8E78-5278EECC75EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ECE2D1-BE59-41D9-825D-D2C8170CA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -1403,7 +1403,9 @@
         <v>30</v>
       </c>
       <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
+      <c r="K15" s="13" t="s">
+        <v>76</v>
+      </c>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F16" s="13"/>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7ECE2D1-BE59-41D9-825D-D2C8170CA65C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42F9615-0916-46D9-BA51-440304BF7F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="5616" yWindow="2508" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -210,9 +210,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>footsteps.mp3</t>
-  </si>
-  <si>
     <t>歩いているときの音</t>
     <rPh sb="0" eb="1">
       <t>アル</t>
@@ -635,6 +632,10 @@
   </si>
   <si>
     <t>OK</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>footsteps.mp3</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1223,13 +1224,13 @@
         <v>46077</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G5" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H5" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -1237,13 +1238,13 @@
         <v>46091</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G6" s="13" t="s">
         <v>8</v>
       </c>
       <c r="H6" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -1311,10 +1312,10 @@
         <v>13</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="K9" s="12" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -1325,7 +1326,7 @@
         <v>16</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I10" s="13" t="s">
         <v>17</v>
@@ -1367,13 +1368,13 @@
         <v>16</v>
       </c>
       <c r="H13" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="I13" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>23</v>
-      </c>
       <c r="J13" s="13" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K13" s="13"/>
     </row>
@@ -1383,10 +1384,10 @@
         <v>16</v>
       </c>
       <c r="H14" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="13" t="s">
         <v>27</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>28</v>
       </c>
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
@@ -1397,14 +1398,14 @@
         <v>16</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J15" s="13"/>
       <c r="K15" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -1413,10 +1414,10 @@
         <v>16</v>
       </c>
       <c r="H16" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="I16" s="13" t="s">
         <v>32</v>
-      </c>
-      <c r="I16" s="13" t="s">
-        <v>33</v>
       </c>
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
@@ -1427,13 +1428,13 @@
         <v>16</v>
       </c>
       <c r="H17" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="I17" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="13" t="s">
-        <v>35</v>
-      </c>
       <c r="J17" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K17" s="13"/>
     </row>
@@ -1443,13 +1444,13 @@
         <v>16</v>
       </c>
       <c r="H18" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="I18" s="13" t="s">
-        <v>37</v>
-      </c>
       <c r="J18" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K18" s="13"/>
     </row>
@@ -1459,13 +1460,13 @@
         <v>16</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="I19" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="J19" s="13" t="s">
         <v>44</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>45</v>
       </c>
       <c r="K19" s="13"/>
     </row>
@@ -1474,21 +1475,21 @@
         <v>46091</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" s="13"/>
       <c r="G20" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H20" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="13" t="s">
         <v>69</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>70</v>
       </c>
       <c r="J20" s="13"/>
       <c r="K20" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -1496,39 +1497,39 @@
         <v>46091</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="I21" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J21" s="13"/>
       <c r="K21" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F22" s="13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G22" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="I22" s="13" t="s">
         <v>41</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>42</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
@@ -1537,44 +1538,44 @@
         <v>16</v>
       </c>
       <c r="H23" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I23" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="I23" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F24" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I24" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J24" s="13"/>
       <c r="K24" s="13"/>
     </row>
     <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F25" s="13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
@@ -1585,42 +1586,42 @@
         <v>16</v>
       </c>
       <c r="H26" s="13" t="s">
+        <v>23</v>
+      </c>
+      <c r="I26" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="I26" s="13" t="s">
-        <v>25</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
     </row>
     <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F27" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
     </row>
     <row r="28" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F28" s="13" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
@@ -1631,28 +1632,28 @@
         <v>16</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I29" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="J29" s="13" t="s">
         <v>63</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>64</v>
       </c>
       <c r="K29" s="13"/>
     </row>
     <row r="30" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
       <c r="F30" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H30" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>53</v>
-      </c>
       <c r="I30" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J30" s="13"/>
       <c r="K30" s="13"/>

--- a/Document/400_DUYDサウンド表.xlsx
+++ b/Document/400_DUYDサウンド表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\新しいフォルダー\Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C42F9615-0916-46D9-BA51-440304BF7F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72AF2542-8AA5-46BE-A834-0EDB8C32596C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5616" yWindow="2508" windowWidth="17280" windowHeight="9960" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{A7C1605A-4F8D-422A-A50A-47C3F46D6375}"/>
   </bookViews>
   <sheets>
     <sheet name="更新履歴" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="80">
   <si>
     <t>更新履歴</t>
     <rPh sb="0" eb="4">
@@ -636,6 +636,36 @@
   </si>
   <si>
     <t>footsteps.mp3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>no_air.mp3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>息切れ音声</t>
+    <rPh sb="0" eb="2">
+      <t>イキギ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>オンセイ</t>
+    </rPh>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>酸素が残り７以下になったら流す</t>
+    <rPh sb="0" eb="2">
+      <t>サンソ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ノコ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ナガ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -894,9 +924,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -934,7 +964,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1040,7 +1070,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1182,7 +1212,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1191,21 +1221,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E2D295A-9295-46AC-88E4-F7ADF9D99499}">
   <dimension ref="B1:H6"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
-    <col min="5" max="5" width="11.19921875" customWidth="1"/>
-    <col min="6" max="6" width="7.296875" customWidth="1"/>
-    <col min="7" max="7" width="11.796875" customWidth="1"/>
+    <col min="5" max="5" width="11.1875" customWidth="1"/>
+    <col min="6" max="6" width="7.3125" customWidth="1"/>
+    <col min="7" max="7" width="11.8125" customWidth="1"/>
     <col min="8" max="8" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.4" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" s="1" customFormat="1" ht="32.25" x14ac:dyDescent="0.7">
       <c r="B1" s="3"/>
       <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E4" s="5" t="s">
         <v>3</v>
       </c>
@@ -1219,7 +1249,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E5" s="15">
         <v>46077</v>
       </c>
@@ -1233,7 +1263,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E6" s="15">
         <v>46091</v>
       </c>
@@ -1255,20 +1285,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DFD89370-1DE1-4DF5-942C-CF8F59DF7864}">
-  <dimension ref="A1:K30"/>
-  <sheetFormatPr defaultColWidth="2.09765625" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultColWidth="2.125" defaultRowHeight="12" customHeight="1" x14ac:dyDescent="0.7"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
     <col min="2" max="2" width="20" style="9" customWidth="1"/>
-    <col min="6" max="6" width="14.09765625" customWidth="1"/>
-    <col min="7" max="7" width="13.09765625" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="13.125" customWidth="1"/>
     <col min="8" max="8" width="32" customWidth="1"/>
-    <col min="9" max="9" width="35.3984375" customWidth="1"/>
-    <col min="10" max="10" width="34.8984375" customWidth="1"/>
+    <col min="9" max="9" width="35.375" customWidth="1"/>
+    <col min="10" max="10" width="34.875" customWidth="1"/>
     <col min="11" max="11" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:11" s="6" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1280,25 +1310,25 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B3" s="11"/>
       <c r="D3" s="10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="E5" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="11.4" customHeight="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:11" ht="11.45" customHeight="1" x14ac:dyDescent="0.7"/>
+    <row r="7" spans="1:11" s="10" customFormat="1" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="B7" s="11"/>
       <c r="D7" s="10" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="25.2" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:11" ht="25.25" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F9" s="12" t="s">
         <v>11</v>
       </c>
@@ -1318,7 +1348,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F10" s="13" t="s">
         <v>15</v>
       </c>
@@ -1334,7 +1364,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="13"/>
     </row>
-    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F11" s="13"/>
       <c r="G11" s="13" t="s">
         <v>16</v>
@@ -1348,7 +1378,7 @@
       <c r="J11" s="13"/>
       <c r="K11" s="13"/>
     </row>
-    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F12" s="13"/>
       <c r="G12" s="13" t="s">
         <v>16</v>
@@ -1362,7 +1392,7 @@
       <c r="J12" s="13"/>
       <c r="K12" s="13"/>
     </row>
-    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F13" s="13"/>
       <c r="G13" s="13" t="s">
         <v>16</v>
@@ -1378,7 +1408,7 @@
       </c>
       <c r="K13" s="13"/>
     </row>
-    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F14" s="13"/>
       <c r="G14" s="13" t="s">
         <v>16</v>
@@ -1392,7 +1422,7 @@
       <c r="J14" s="13"/>
       <c r="K14" s="13"/>
     </row>
-    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F15" s="13"/>
       <c r="G15" s="13" t="s">
         <v>16</v>
@@ -1408,7 +1438,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F16" s="13"/>
       <c r="G16" s="13" t="s">
         <v>16</v>
@@ -1422,7 +1452,7 @@
       <c r="J16" s="13"/>
       <c r="K16" s="13"/>
     </row>
-    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F17" s="13"/>
       <c r="G17" s="13" t="s">
         <v>16</v>
@@ -1438,7 +1468,7 @@
       </c>
       <c r="K17" s="13"/>
     </row>
-    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F18" s="13"/>
       <c r="G18" s="13" t="s">
         <v>16</v>
@@ -1454,7 +1484,7 @@
       </c>
       <c r="K18" s="13"/>
     </row>
-    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F19" s="13"/>
       <c r="G19" s="13" t="s">
         <v>16</v>
@@ -1470,7 +1500,7 @@
       </c>
       <c r="K19" s="13"/>
     </row>
-    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="A20" s="14">
         <v>46091</v>
       </c>
@@ -1492,171 +1522,188 @@
         <v>75</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A21" s="14">
-        <v>46091</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>71</v>
-      </c>
+    <row r="21" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A21" s="14"/>
       <c r="F21" s="13"/>
       <c r="G21" s="13" t="s">
         <v>16</v>
       </c>
       <c r="H21" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="I21" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="J21" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="K21" s="13"/>
+    </row>
+    <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="A22" s="14">
+        <v>46091</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H22" s="13" t="s">
         <v>67</v>
       </c>
-      <c r="I21" s="13" t="s">
+      <c r="I22" s="13" t="s">
         <v>70</v>
-      </c>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F22" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="I22" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="J22" s="13"/>
       <c r="K22" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F23" s="13"/>
+    <row r="23" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F23" s="13" t="s">
+        <v>37</v>
+      </c>
       <c r="G23" s="13" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="I23" s="13" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J23" s="13"/>
       <c r="K23" s="13" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F24" s="13" t="s">
+    <row r="24" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F24" s="13"/>
+      <c r="G24" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="I24" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="J24" s="13"/>
+      <c r="K24" s="13" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F25" s="13" t="s">
         <v>47</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="J24" s="13"/>
-      <c r="K24" s="13"/>
-    </row>
-    <row r="25" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F25" s="13" t="s">
-        <v>48</v>
       </c>
       <c r="G25" s="13" t="s">
         <v>40</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I25" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J25" s="13"/>
       <c r="K25" s="13"/>
     </row>
-    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F26" s="13"/>
+    <row r="26" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F26" s="13" t="s">
+        <v>48</v>
+      </c>
       <c r="G26" s="13" t="s">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="I26" s="13" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="J26" s="13"/>
       <c r="K26" s="13"/>
     </row>
-    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F27" s="13" t="s">
-        <v>49</v>
-      </c>
+    <row r="27" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F27" s="13"/>
       <c r="G27" s="13" t="s">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="I27" s="13" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="J27" s="13"/>
       <c r="K27" s="13"/>
     </row>
-    <row r="28" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
       <c r="F28" s="13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>40</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="I28" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J28" s="13"/>
       <c r="K28" s="13"/>
     </row>
-    <row r="29" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F29" s="13"/>
+    <row r="29" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F29" s="13" t="s">
+        <v>50</v>
+      </c>
       <c r="G29" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="I29" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+    </row>
+    <row r="30" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F30" s="13"/>
+      <c r="G30" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H29" s="13" t="s">
+      <c r="H30" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="I29" s="13" t="s">
+      <c r="I30" s="13" t="s">
         <v>62</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J30" s="13" t="s">
         <v>63</v>
       </c>
-      <c r="K29" s="13"/>
-    </row>
-    <row r="30" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="F30" s="13" t="s">
+      <c r="K30" s="13"/>
+    </row>
+    <row r="31" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.7">
+      <c r="F31" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="G31" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H30" s="13" t="s">
+      <c r="H31" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="13" t="s">
+      <c r="I31" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="J30" s="13"/>
-      <c r="K30" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
